--- a/flaskapp1/chon_quat.xlsx
+++ b/flaskapp1/chon_quat.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MKC\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MKC\Downloads\flask-thung-than-main\flask-thung-than-main\flaskapp1\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="58">
   <si>
     <t>Model</t>
   </si>
@@ -56,7 +56,148 @@
     <t>SCI-H10</t>
   </si>
   <si>
-    <t>SCI-H11</t>
+    <t>SCI-H12</t>
+  </si>
+  <si>
+    <t>SCI-H13</t>
+  </si>
+  <si>
+    <t>SCI-H14</t>
+  </si>
+  <si>
+    <t>SCI-H16</t>
+  </si>
+  <si>
+    <t>SCI-H5</t>
+  </si>
+  <si>
+    <t>SCI-H5.5</t>
+  </si>
+  <si>
+    <t>SCI-H6.3</t>
+  </si>
+  <si>
+    <t>SCI-H7</t>
+  </si>
+  <si>
+    <t>SCI-H8</t>
+  </si>
+  <si>
+    <t>SCI-D3.2</t>
+  </si>
+  <si>
+    <t>SCI-D3.8</t>
+  </si>
+  <si>
+    <t>SCI-D4</t>
+  </si>
+  <si>
+    <t>SCI-D5</t>
+  </si>
+  <si>
+    <t>SCI-D5.5</t>
+  </si>
+  <si>
+    <t>SCI-D6.3</t>
+  </si>
+  <si>
+    <t>SCI-D7</t>
+  </si>
+  <si>
+    <t>SCI-D8</t>
+  </si>
+  <si>
+    <t>SCI-D10</t>
+  </si>
+  <si>
+    <t>SCI-D12</t>
+  </si>
+  <si>
+    <t>SCI-D14</t>
+  </si>
+  <si>
+    <t>Trực tiếp</t>
+  </si>
+  <si>
+    <t>SCD-B2.8</t>
+  </si>
+  <si>
+    <t>SCD-B3.2</t>
+  </si>
+  <si>
+    <t>SCD-B3.8</t>
+  </si>
+  <si>
+    <t>SCD-B4</t>
+  </si>
+  <si>
+    <t>SCD-B5</t>
+  </si>
+  <si>
+    <t>SCD-B5.5</t>
+  </si>
+  <si>
+    <t>SCD-B6.3</t>
+  </si>
+  <si>
+    <t>SCD-B7</t>
+  </si>
+  <si>
+    <t>SCD-B8</t>
+  </si>
+  <si>
+    <t>SCD-B10</t>
+  </si>
+  <si>
+    <t>SCD-B11</t>
+  </si>
+  <si>
+    <t>SCD-B12</t>
+  </si>
+  <si>
+    <t>SCD-B12.5</t>
+  </si>
+  <si>
+    <t>SCD-B12.9</t>
+  </si>
+  <si>
+    <t>SAD-C3</t>
+  </si>
+  <si>
+    <t>SAD-C4</t>
+  </si>
+  <si>
+    <t>SAD-C5</t>
+  </si>
+  <si>
+    <t>SAD-C6</t>
+  </si>
+  <si>
+    <t>SAD-C7</t>
+  </si>
+  <si>
+    <t>SAD-C8</t>
+  </si>
+  <si>
+    <t>SAD-C9</t>
+  </si>
+  <si>
+    <t>SAD-C10</t>
+  </si>
+  <si>
+    <t>SAD-C11</t>
+  </si>
+  <si>
+    <t>SAD-C12</t>
+  </si>
+  <si>
+    <t>SAD-C13</t>
+  </si>
+  <si>
+    <t>SAD-C14</t>
+  </si>
+  <si>
+    <t>Hướng trục</t>
   </si>
 </sst>
 </file>
@@ -121,17 +262,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -412,114 +554,2041 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
     <col min="2" max="2" width="14.28515625" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="1">
+        <v>10000</v>
+      </c>
+      <c r="D2" s="1">
+        <v>12000</v>
+      </c>
+      <c r="E2" s="1">
+        <v>2700</v>
+      </c>
+      <c r="F2" s="1">
+        <v>3500</v>
+      </c>
+      <c r="G2" s="1">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1">
+        <v>12000</v>
+      </c>
+      <c r="D3" s="1">
+        <v>14000</v>
+      </c>
+      <c r="E3" s="1">
+        <v>2700</v>
+      </c>
+      <c r="F3" s="1">
+        <v>3500</v>
+      </c>
+      <c r="G3" s="1">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="1">
+        <v>10000</v>
+      </c>
+      <c r="D4" s="1">
+        <v>15000</v>
+      </c>
+      <c r="E4" s="1">
+        <v>2800</v>
+      </c>
+      <c r="F4" s="1">
+        <v>3800</v>
+      </c>
+      <c r="G4" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="1">
+        <v>14000</v>
+      </c>
+      <c r="D5" s="1">
+        <v>18000</v>
+      </c>
+      <c r="E5" s="1">
+        <v>2900</v>
+      </c>
+      <c r="F5" s="1">
+        <v>4000</v>
+      </c>
+      <c r="G5" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="1">
+        <v>16000</v>
+      </c>
+      <c r="D6" s="1">
+        <v>22000</v>
+      </c>
+      <c r="E6" s="1">
+        <v>3000</v>
+      </c>
+      <c r="F6" s="1">
+        <v>4200</v>
+      </c>
+      <c r="G6" s="1">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="1">
+        <v>18000</v>
+      </c>
+      <c r="D7" s="1">
+        <v>24000</v>
+      </c>
+      <c r="E7" s="1">
+        <v>3200</v>
+      </c>
+      <c r="F7" s="1">
+        <v>4500</v>
+      </c>
+      <c r="G7" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="1">
+        <v>22000</v>
+      </c>
+      <c r="D8" s="1">
+        <v>28000</v>
+      </c>
+      <c r="E8" s="1">
+        <v>3200</v>
+      </c>
+      <c r="F8" s="1">
+        <v>4300</v>
+      </c>
+      <c r="G8" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="1">
+        <v>24000</v>
+      </c>
+      <c r="D9" s="1">
+        <v>30000</v>
+      </c>
+      <c r="E9" s="1">
+        <v>3200</v>
+      </c>
+      <c r="F9" s="1">
+        <v>4500</v>
+      </c>
+      <c r="G9" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="1">
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="1">
+        <v>26000</v>
+      </c>
+      <c r="D10" s="1">
         <v>34000</v>
       </c>
-      <c r="D2" s="1">
+      <c r="E10" s="1">
+        <v>3200</v>
+      </c>
+      <c r="F10" s="1">
+        <v>4500</v>
+      </c>
+      <c r="G10" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="1">
+        <v>34000</v>
+      </c>
+      <c r="D11" s="1">
         <v>38000</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E11" s="1">
         <v>3300</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F11" s="1">
         <v>4500</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G11" s="1">
         <v>37</v>
       </c>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="1">
+      <c r="B12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="1">
+        <v>33000</v>
+      </c>
+      <c r="D12" s="1">
         <v>40000</v>
       </c>
-      <c r="D3" s="1">
+      <c r="E12" s="1">
+        <v>3300</v>
+      </c>
+      <c r="F12" s="1">
+        <v>4500</v>
+      </c>
+      <c r="G12" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="1">
+        <v>38000</v>
+      </c>
+      <c r="D13" s="1">
+        <v>45000</v>
+      </c>
+      <c r="E13" s="1">
+        <v>3300</v>
+      </c>
+      <c r="F13" s="1">
+        <v>4500</v>
+      </c>
+      <c r="G13" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="1">
+        <v>40000</v>
+      </c>
+      <c r="D14" s="1">
         <v>50000</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E14" s="1">
+        <v>3400</v>
+      </c>
+      <c r="F14" s="1">
+        <v>4500</v>
+      </c>
+      <c r="G14" s="1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="1">
+        <v>50000</v>
+      </c>
+      <c r="D15" s="1">
+        <v>60000</v>
+      </c>
+      <c r="E15" s="1">
+        <v>3500</v>
+      </c>
+      <c r="F15" s="1">
+        <v>4600</v>
+      </c>
+      <c r="G15" s="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="1">
+        <v>60000</v>
+      </c>
+      <c r="D16" s="1">
+        <v>66000</v>
+      </c>
+      <c r="E16" s="1">
+        <v>3500</v>
+      </c>
+      <c r="F16" s="1">
+        <v>4600</v>
+      </c>
+      <c r="G16" s="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="1">
+        <v>65000</v>
+      </c>
+      <c r="D17" s="1">
+        <v>72000</v>
+      </c>
+      <c r="E17" s="1">
+        <v>3500</v>
+      </c>
+      <c r="F17" s="1">
+        <v>4600</v>
+      </c>
+      <c r="G17" s="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="1">
+        <v>70000</v>
+      </c>
+      <c r="D18" s="1">
+        <v>80000</v>
+      </c>
+      <c r="E18" s="1">
+        <v>3500</v>
+      </c>
+      <c r="F18" s="1">
+        <v>4600</v>
+      </c>
+      <c r="G18" s="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="1">
+        <v>78000</v>
+      </c>
+      <c r="D19" s="1">
+        <v>90000</v>
+      </c>
+      <c r="E19" s="1">
+        <v>3300</v>
+      </c>
+      <c r="F19" s="1">
+        <v>4700</v>
+      </c>
+      <c r="G19" s="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="1">
+        <v>90000</v>
+      </c>
+      <c r="D20" s="1">
+        <v>100000</v>
+      </c>
+      <c r="E20" s="1">
+        <v>3500</v>
+      </c>
+      <c r="F20" s="1">
+        <v>5000</v>
+      </c>
+      <c r="G20" s="1">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="1">
+        <v>100000</v>
+      </c>
+      <c r="D21" s="1">
+        <v>110000</v>
+      </c>
+      <c r="E21" s="1">
+        <v>3300</v>
+      </c>
+      <c r="F21" s="1">
+        <v>4700</v>
+      </c>
+      <c r="G21" s="1">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="1">
+        <v>110000</v>
+      </c>
+      <c r="D22" s="1">
+        <v>120000</v>
+      </c>
+      <c r="E22" s="1">
+        <v>3500</v>
+      </c>
+      <c r="F22" s="1">
+        <v>5000</v>
+      </c>
+      <c r="G22" s="1">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="1">
+        <v>120000</v>
+      </c>
+      <c r="D23" s="1">
+        <v>150000</v>
+      </c>
+      <c r="E23" s="1">
+        <v>3500</v>
+      </c>
+      <c r="F23" s="1">
+        <v>5200</v>
+      </c>
+      <c r="G23" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="1">
+        <v>150000</v>
+      </c>
+      <c r="D24" s="1">
+        <v>190000</v>
+      </c>
+      <c r="E24" s="1">
+        <v>3800</v>
+      </c>
+      <c r="F24" s="1">
+        <v>5500</v>
+      </c>
+      <c r="G24" s="1">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="3">
+        <v>100</v>
+      </c>
+      <c r="D25" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E25" s="3">
+        <v>400</v>
+      </c>
+      <c r="F25" s="3">
+        <v>800</v>
+      </c>
+      <c r="G25" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="1">
+        <v>2000</v>
+      </c>
+      <c r="D26" s="1">
         <v>3000</v>
       </c>
-      <c r="F3" s="1">
+      <c r="E26" s="1">
+        <v>400</v>
+      </c>
+      <c r="F26" s="1">
+        <v>800</v>
+      </c>
+      <c r="G26" s="1">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="1">
+        <v>3000</v>
+      </c>
+      <c r="D27" s="1">
         <v>4500</v>
       </c>
-      <c r="G3" s="1">
+      <c r="E27" s="1">
+        <v>400</v>
+      </c>
+      <c r="F27" s="1">
+        <v>800</v>
+      </c>
+      <c r="G27" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="1">
+        <v>4000</v>
+      </c>
+      <c r="D28" s="1">
+        <v>5500</v>
+      </c>
+      <c r="E28" s="1">
+        <v>450</v>
+      </c>
+      <c r="F28" s="1">
+        <v>900</v>
+      </c>
+      <c r="G28" s="1">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="1">
+        <v>4500</v>
+      </c>
+      <c r="D29" s="1">
+        <v>6500</v>
+      </c>
+      <c r="E29" s="1">
+        <v>450</v>
+      </c>
+      <c r="F29" s="1">
+        <v>1000</v>
+      </c>
+      <c r="G29" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="1">
+        <v>5500</v>
+      </c>
+      <c r="D30" s="1">
+        <v>8500</v>
+      </c>
+      <c r="E30" s="1">
+        <v>500</v>
+      </c>
+      <c r="F30" s="1">
+        <v>1200</v>
+      </c>
+      <c r="G30" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="1">
+        <v>7000</v>
+      </c>
+      <c r="D31" s="1">
+        <v>11000</v>
+      </c>
+      <c r="E31" s="1">
+        <v>500</v>
+      </c>
+      <c r="F31" s="1">
+        <v>1250</v>
+      </c>
+      <c r="G31" s="1">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="1">
+        <v>9000</v>
+      </c>
+      <c r="D32" s="1">
+        <v>14000</v>
+      </c>
+      <c r="E32" s="1">
+        <v>550</v>
+      </c>
+      <c r="F32" s="1">
+        <v>1300</v>
+      </c>
+      <c r="G32" s="1">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="1">
+        <v>14000</v>
+      </c>
+      <c r="D33" s="1">
+        <v>18000</v>
+      </c>
+      <c r="E33" s="1">
+        <v>600</v>
+      </c>
+      <c r="F33" s="1">
+        <v>1800</v>
+      </c>
+      <c r="G33" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="1">
+        <v>15000</v>
+      </c>
+      <c r="D34" s="1">
+        <v>21000</v>
+      </c>
+      <c r="E34" s="1">
+        <v>700</v>
+      </c>
+      <c r="F34" s="1">
+        <v>1850</v>
+      </c>
+      <c r="G34" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="1">
+        <v>19000</v>
+      </c>
+      <c r="D35" s="1">
+        <v>22000</v>
+      </c>
+      <c r="E35" s="1">
+        <v>800</v>
+      </c>
+      <c r="F35" s="1">
+        <v>2300</v>
+      </c>
+      <c r="G35" s="1">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="1">
+        <v>21000</v>
+      </c>
+      <c r="D36" s="1">
+        <v>27000</v>
+      </c>
+      <c r="E36" s="1">
+        <v>850</v>
+      </c>
+      <c r="F36" s="1">
+        <v>2600</v>
+      </c>
+      <c r="G36" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="1">
+        <v>28000</v>
+      </c>
+      <c r="D37" s="1">
+        <v>32000</v>
+      </c>
+      <c r="E37" s="1">
+        <v>1200</v>
+      </c>
+      <c r="F37" s="1">
+        <v>2800</v>
+      </c>
+      <c r="G37" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="1">
+        <v>31000</v>
+      </c>
+      <c r="D38" s="1">
+        <v>35000</v>
+      </c>
+      <c r="E38" s="1">
+        <v>1400</v>
+      </c>
+      <c r="F38" s="1">
+        <v>3000</v>
+      </c>
+      <c r="G38" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="1">
+        <v>33000</v>
+      </c>
+      <c r="D39" s="1">
+        <v>38000</v>
+      </c>
+      <c r="E39" s="1">
+        <v>1450</v>
+      </c>
+      <c r="F39" s="1">
+        <v>3000</v>
+      </c>
+      <c r="G39" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="1">
+        <v>35000</v>
+      </c>
+      <c r="D40" s="1">
+        <v>42000</v>
+      </c>
+      <c r="E40" s="1">
+        <v>1500</v>
+      </c>
+      <c r="F40" s="1">
+        <v>3000</v>
+      </c>
+      <c r="G40" s="1">
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="1">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="1">
+        <v>45000</v>
+      </c>
+      <c r="D41" s="1">
+        <v>55000</v>
+      </c>
+      <c r="E41" s="1">
+        <v>1800</v>
+      </c>
+      <c r="F41" s="1">
+        <v>3000</v>
+      </c>
+      <c r="G41" s="1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="1">
+        <v>54000</v>
+      </c>
+      <c r="D42" s="1">
+        <v>65000</v>
+      </c>
+      <c r="E42" s="1">
+        <v>2000</v>
+      </c>
+      <c r="F42" s="1">
+        <v>3000</v>
+      </c>
+      <c r="G42" s="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="1">
+        <v>64000</v>
+      </c>
+      <c r="D43" s="1">
+        <v>73000</v>
+      </c>
+      <c r="E43" s="1">
+        <v>2100</v>
+      </c>
+      <c r="F43" s="1">
+        <v>3200</v>
+      </c>
+      <c r="G43" s="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" s="1">
+        <v>73000</v>
+      </c>
+      <c r="D44" s="1">
+        <v>80000</v>
+      </c>
+      <c r="E44" s="1">
+        <v>2300</v>
+      </c>
+      <c r="F44" s="1">
+        <v>3200</v>
+      </c>
+      <c r="G44" s="1">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" s="1">
+        <v>80000</v>
+      </c>
+      <c r="D45" s="1">
+        <v>95000</v>
+      </c>
+      <c r="E45" s="1">
+        <v>2500</v>
+      </c>
+      <c r="F45" s="1">
+        <v>3200</v>
+      </c>
+      <c r="G45" s="1">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C46" s="1">
+        <v>900</v>
+      </c>
+      <c r="D46" s="1">
+        <v>1500</v>
+      </c>
+      <c r="E46" s="1">
+        <v>150</v>
+      </c>
+      <c r="F46" s="1">
+        <v>350</v>
+      </c>
+      <c r="G46" s="1">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C47" s="1">
+        <v>1500</v>
+      </c>
+      <c r="D47" s="1">
+        <v>2200</v>
+      </c>
+      <c r="E47" s="1">
+        <v>150</v>
+      </c>
+      <c r="F47" s="1">
+        <v>450</v>
+      </c>
+      <c r="G47" s="1">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C48" s="1">
+        <v>2200</v>
+      </c>
+      <c r="D48" s="1">
+        <v>3200</v>
+      </c>
+      <c r="E48" s="1">
+        <v>200</v>
+      </c>
+      <c r="F48" s="1">
+        <v>550</v>
+      </c>
+      <c r="G48" s="1">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C49" s="1">
+        <v>3300</v>
+      </c>
+      <c r="D49" s="1">
+        <v>5000</v>
+      </c>
+      <c r="E49" s="1">
+        <v>220</v>
+      </c>
+      <c r="F49" s="1">
+        <v>600</v>
+      </c>
+      <c r="G49" s="1">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C50" s="1">
+        <v>5000</v>
+      </c>
+      <c r="D50" s="1">
+        <v>9000</v>
+      </c>
+      <c r="E50" s="1">
+        <v>230</v>
+      </c>
+      <c r="F50" s="1">
+        <v>650</v>
+      </c>
+      <c r="G50" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C51" s="1">
+        <v>9000</v>
+      </c>
+      <c r="D51" s="1">
+        <v>11000</v>
+      </c>
+      <c r="E51" s="1">
+        <v>250</v>
+      </c>
+      <c r="F51" s="1">
+        <v>660</v>
+      </c>
+      <c r="G51" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C52" s="1">
+        <v>10000</v>
+      </c>
+      <c r="D52" s="1">
+        <v>13000</v>
+      </c>
+      <c r="E52" s="1">
+        <v>250</v>
+      </c>
+      <c r="F52" s="1">
+        <v>600</v>
+      </c>
+      <c r="G52" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C53" s="1">
+        <v>11000</v>
+      </c>
+      <c r="D53" s="1">
+        <v>15000</v>
+      </c>
+      <c r="E53" s="1">
+        <v>250</v>
+      </c>
+      <c r="F53" s="1">
+        <v>700</v>
+      </c>
+      <c r="G53" s="1">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C54" s="1">
+        <v>13000</v>
+      </c>
+      <c r="D54" s="1">
+        <v>19000</v>
+      </c>
+      <c r="E54" s="1">
+        <v>280</v>
+      </c>
+      <c r="F54" s="1">
+        <v>720</v>
+      </c>
+      <c r="G54" s="1">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C55" s="1">
+        <v>20000</v>
+      </c>
+      <c r="D55" s="1">
+        <v>27000</v>
+      </c>
+      <c r="E55" s="1">
+        <v>300</v>
+      </c>
+      <c r="F55" s="1">
+        <v>750</v>
+      </c>
+      <c r="G55" s="1">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C56" s="1">
+        <v>27000</v>
+      </c>
+      <c r="D56" s="1">
+        <v>40000</v>
+      </c>
+      <c r="E56" s="1">
+        <v>320</v>
+      </c>
+      <c r="F56" s="1">
+        <v>1000</v>
+      </c>
+      <c r="G56" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C57" s="1">
+        <v>38000</v>
+      </c>
+      <c r="D57" s="1">
         <v>50000</v>
       </c>
-      <c r="D4" s="1">
+      <c r="E57" s="1">
+        <v>330</v>
+      </c>
+      <c r="F57" s="1">
+        <v>1100</v>
+      </c>
+      <c r="G57" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C58" s="1">
+        <v>48000</v>
+      </c>
+      <c r="D58" s="1">
+        <v>55000</v>
+      </c>
+      <c r="E58" s="1">
+        <v>250</v>
+      </c>
+      <c r="F58" s="1">
+        <v>1000</v>
+      </c>
+      <c r="G58" s="1">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C59" s="1">
+        <v>50000</v>
+      </c>
+      <c r="D59" s="1">
         <v>65000</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E59" s="1">
+        <v>550</v>
+      </c>
+      <c r="F59" s="1">
+        <v>1100</v>
+      </c>
+      <c r="G59" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C60" s="1">
+        <v>62000</v>
+      </c>
+      <c r="D60" s="1">
+        <v>75000</v>
+      </c>
+      <c r="E60" s="1">
+        <v>400</v>
+      </c>
+      <c r="F60" s="1">
+        <v>1250</v>
+      </c>
+      <c r="G60" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C61" s="1">
+        <v>65000</v>
+      </c>
+      <c r="D61" s="1">
+        <v>85000</v>
+      </c>
+      <c r="E61" s="1">
+        <v>400</v>
+      </c>
+      <c r="F61" s="1">
+        <v>1250</v>
+      </c>
+      <c r="G61" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C62" s="3">
+        <v>80000</v>
+      </c>
+      <c r="D62" s="3">
+        <v>105000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>600</v>
+      </c>
+      <c r="F62" s="3">
+        <v>1450</v>
+      </c>
+      <c r="G62" s="3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C63" s="1">
+        <v>1000</v>
+      </c>
+      <c r="D63" s="1">
+        <v>2000</v>
+      </c>
+      <c r="E63" s="1">
+        <v>80</v>
+      </c>
+      <c r="F63" s="1">
+        <v>140</v>
+      </c>
+      <c r="G63" s="1">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C64" s="1">
+        <v>2000</v>
+      </c>
+      <c r="D64" s="1">
         <v>3000</v>
       </c>
-      <c r="F4" s="1">
+      <c r="E64" s="1">
+        <v>100</v>
+      </c>
+      <c r="F64" s="1">
+        <v>180</v>
+      </c>
+      <c r="G64" s="1">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C65" s="1">
+        <v>2500</v>
+      </c>
+      <c r="D65" s="1">
+        <v>3800</v>
+      </c>
+      <c r="E65" s="1">
+        <v>150</v>
+      </c>
+      <c r="F65" s="1">
+        <v>250</v>
+      </c>
+      <c r="G65" s="1">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C66" s="1">
+        <v>3200</v>
+      </c>
+      <c r="D66" s="1">
+        <v>4500</v>
+      </c>
+      <c r="E66" s="1">
+        <v>200</v>
+      </c>
+      <c r="F66" s="1">
+        <v>250</v>
+      </c>
+      <c r="G66" s="1">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C67" s="1">
         <v>5000</v>
       </c>
-      <c r="G4" s="1">
+      <c r="D67" s="1">
+        <v>8000</v>
+      </c>
+      <c r="E67" s="1">
+        <v>150</v>
+      </c>
+      <c r="F67" s="1">
+        <v>250</v>
+      </c>
+      <c r="G67" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C68" s="1">
+        <v>6800</v>
+      </c>
+      <c r="D68" s="1">
+        <v>9000</v>
+      </c>
+      <c r="E68" s="1">
+        <v>200</v>
+      </c>
+      <c r="F68" s="1">
+        <v>350</v>
+      </c>
+      <c r="G68" s="1">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C69" s="1">
+        <v>9000</v>
+      </c>
+      <c r="D69" s="1">
+        <v>15000</v>
+      </c>
+      <c r="E69" s="1">
+        <v>150</v>
+      </c>
+      <c r="F69" s="1">
+        <v>350</v>
+      </c>
+      <c r="G69" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C70" s="1">
+        <v>12000</v>
+      </c>
+      <c r="D70" s="1">
+        <v>19500</v>
+      </c>
+      <c r="E70" s="1">
+        <v>200</v>
+      </c>
+      <c r="F70" s="1">
+        <v>450</v>
+      </c>
+      <c r="G70" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C71" s="1">
+        <v>19000</v>
+      </c>
+      <c r="D71" s="1">
+        <v>27000</v>
+      </c>
+      <c r="E71" s="1">
+        <v>250</v>
+      </c>
+      <c r="F71" s="1">
+        <v>450</v>
+      </c>
+      <c r="G71" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C72" s="1">
+        <v>25000</v>
+      </c>
+      <c r="D72" s="1">
+        <v>32000</v>
+      </c>
+      <c r="E72" s="1">
+        <v>250</v>
+      </c>
+      <c r="F72" s="1">
+        <v>550</v>
+      </c>
+      <c r="G72" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C73" s="1">
+        <v>32000</v>
+      </c>
+      <c r="D73" s="1">
+        <v>40000</v>
+      </c>
+      <c r="E73" s="1">
+        <v>300</v>
+      </c>
+      <c r="F73" s="1">
+        <v>600</v>
+      </c>
+      <c r="G73" s="1">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C74" s="1">
+        <v>35000</v>
+      </c>
+      <c r="D74" s="1">
+        <v>45000</v>
+      </c>
+      <c r="E74" s="1">
+        <v>350</v>
+      </c>
+      <c r="F74" s="1">
+        <v>650</v>
+      </c>
+      <c r="G74" s="1">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C75" s="1">
+        <v>42000</v>
+      </c>
+      <c r="D75" s="1">
+        <v>50000</v>
+      </c>
+      <c r="E75" s="1">
+        <v>300</v>
+      </c>
+      <c r="F75" s="1">
+        <v>680</v>
+      </c>
+      <c r="G75" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C76" s="1">
+        <v>48000</v>
+      </c>
+      <c r="D76" s="1">
+        <v>55000</v>
+      </c>
+      <c r="E76" s="1">
+        <v>350</v>
+      </c>
+      <c r="F76" s="1">
+        <v>710</v>
+      </c>
+      <c r="G76" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C77" s="1">
+        <v>50000</v>
+      </c>
+      <c r="D77" s="1">
+        <v>60000</v>
+      </c>
+      <c r="E77" s="1">
+        <v>400</v>
+      </c>
+      <c r="F77" s="1">
+        <v>850</v>
+      </c>
+      <c r="G77" s="1">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C78" s="1">
+        <v>60000</v>
+      </c>
+      <c r="D78" s="1">
+        <v>78000</v>
+      </c>
+      <c r="E78" s="1">
+        <v>400</v>
+      </c>
+      <c r="F78" s="1">
+        <v>1000</v>
+      </c>
+      <c r="G78" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C79" s="1">
+        <v>52000</v>
+      </c>
+      <c r="D79" s="1">
+        <v>65000</v>
+      </c>
+      <c r="E79" s="1">
+        <v>350</v>
+      </c>
+      <c r="F79" s="1">
+        <v>750</v>
+      </c>
+      <c r="G79" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C80" s="1">
+        <v>65000</v>
+      </c>
+      <c r="D80" s="1">
+        <v>80000</v>
+      </c>
+      <c r="E80" s="1">
+        <v>350</v>
+      </c>
+      <c r="F80" s="1">
+        <v>780</v>
+      </c>
+      <c r="G80" s="1">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C81" s="1">
+        <v>70000</v>
+      </c>
+      <c r="D81" s="1">
+        <v>90000</v>
+      </c>
+      <c r="E81" s="1">
+        <v>400</v>
+      </c>
+      <c r="F81" s="1">
+        <v>1050</v>
+      </c>
+      <c r="G81" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C82" s="1">
+        <v>85000</v>
+      </c>
+      <c r="D82" s="1">
+        <v>100000</v>
+      </c>
+      <c r="E82" s="1">
+        <v>400</v>
+      </c>
+      <c r="F82" s="1">
+        <v>1100</v>
+      </c>
+      <c r="G82" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C83" s="1">
+        <v>85000</v>
+      </c>
+      <c r="D83" s="1">
+        <v>110000</v>
+      </c>
+      <c r="E83" s="1">
+        <v>300</v>
+      </c>
+      <c r="F83" s="1">
+        <v>920</v>
+      </c>
+      <c r="G83" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C84" s="1">
+        <v>115000</v>
+      </c>
+      <c r="D84" s="1">
+        <v>130000</v>
+      </c>
+      <c r="E84" s="1">
+        <v>300</v>
+      </c>
+      <c r="F84" s="1">
+        <v>1200</v>
+      </c>
+      <c r="G84" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C85" s="1">
+        <v>110000</v>
+      </c>
+      <c r="D85" s="1">
+        <v>130000</v>
+      </c>
+      <c r="E85" s="1">
+        <v>320</v>
+      </c>
+      <c r="F85" s="1">
+        <v>1100</v>
+      </c>
+      <c r="G85" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C86" s="1">
+        <v>130000</v>
+      </c>
+      <c r="D86" s="1">
+        <v>145000</v>
+      </c>
+      <c r="E86" s="1">
+        <v>350</v>
+      </c>
+      <c r="F86" s="1">
+        <v>1200</v>
+      </c>
+      <c r="G86" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
         <v>55</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C87" s="1">
+        <v>145000</v>
+      </c>
+      <c r="D87" s="1">
+        <v>170000</v>
+      </c>
+      <c r="E87" s="1">
+        <v>450</v>
+      </c>
+      <c r="F87" s="1">
+        <v>1200</v>
+      </c>
+      <c r="G87" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C88" s="1">
+        <v>150000</v>
+      </c>
+      <c r="D88" s="1">
+        <v>180000</v>
+      </c>
+      <c r="E88" s="1">
+        <v>550</v>
+      </c>
+      <c r="F88" s="1">
+        <v>1250</v>
+      </c>
+      <c r="G88" s="1">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>